--- a/data/trans_orig/P04B3_3_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_3_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su vivienda tiene goteras, humedades en paredes, suelos, techos o cimientos, o podredumbre en suelos, marcos de ventanas o puertas en 2023</t>
+          <t>Población según si su vivienda tiene goteras, humedades en paredes, suelos, techos o cimientos, o podredumbre en suelos, marcos de ventanas o puertas en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16952</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8494</t>
+          <t>8006</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22591</t>
+          <t>23627</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58426</t>
+          <t>56430</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97752</t>
+          <t>97823</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41793</t>
+          <t>41853</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69834</t>
+          <t>68731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109611</t>
+          <t>108806</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>157794</t>
+          <t>158621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>529773</t>
+          <t>528574</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>569950</t>
+          <t>571745</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>648377</t>
+          <t>649956</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>676915</t>
+          <t>677799</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1188623</t>
+          <t>1187514</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1238370</t>
+          <t>1238979</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24149</t>
+          <t>24600</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18395</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>15307</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36576</t>
+          <t>37390</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39137</t>
+          <t>38350</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100906</t>
+          <t>103263</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>75897</t>
+          <t>74941</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>109086</t>
+          <t>107251</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>107812</t>
+          <t>113263</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>195526</t>
+          <t>198113</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1074333</t>
+          <t>1072599</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1146919</t>
+          <t>1148332</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>835604</t>
+          <t>836692</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>869745</t>
+          <t>870884</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1925510</t>
+          <t>1923304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2026941</t>
+          <t>2023420</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26190</t>
+          <t>31997</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>5416</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20368</t>
+          <t>20856</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>14048</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40512</t>
+          <t>38852</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24994</t>
+          <t>25702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50531</t>
+          <t>51654</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54540</t>
+          <t>55855</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>543026</t>
+          <t>582036</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89957</t>
+          <t>90172</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>723634</t>
+          <t>732332</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>638525</t>
+          <t>634354</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>669501</t>
+          <t>669047</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>381536</t>
+          <t>344475</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>863269</t>
+          <t>861968</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>894229</t>
+          <t>886162</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1520778</t>
+          <t>1519288</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11335</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31492</t>
+          <t>31900</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14537</t>
+          <t>14861</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45330</t>
+          <t>45341</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30081</t>
+          <t>28611</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64924</t>
+          <t>63885</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54787</t>
+          <t>52473</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87070</t>
+          <t>86253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65447</t>
+          <t>68640</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107440</t>
+          <t>107726</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>133532</t>
+          <t>133019</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>184358</t>
+          <t>182553</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>816407</t>
+          <t>818444</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>854875</t>
+          <t>854721</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>957954</t>
+          <t>958365</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1007395</t>
+          <t>1006366</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1787233</t>
+          <t>1789463</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1847630</t>
+          <t>1850304</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,6%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37661</t>
+          <t>36415</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73256</t>
+          <t>72470</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39789</t>
+          <t>39343</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>76178</t>
+          <t>74477</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85746</t>
+          <t>83956</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>133233</t>
+          <t>132048</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>199841</t>
+          <t>196839</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>293535</t>
+          <t>290678</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>290415</t>
+          <t>286061</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1168481</t>
+          <t>1100430</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>531560</t>
+          <t>533205</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1493205</t>
+          <t>1399155</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3107973</t>
+          <t>3110816</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3219287</t>
+          <t>3222062</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2494813</t>
+          <t>2564264</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3364277</t>
+          <t>3366754</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5594783</t>
+          <t>5702669</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6533290</t>
+          <t>6531483</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B3_3_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_3_2023-Habitat-trans_orig.xlsx
@@ -725,22 +725,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16180</t>
+          <t>16871</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11802</t>
+          <t>12225</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14059</t>
+          <t>15112</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>8958</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23627</t>
+          <t>23664</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>75414</t>
+          <t>84426</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56430</t>
+          <t>66654</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>97823</t>
+          <t>107398</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>56385</t>
+          <t>63727</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41853</t>
+          <t>51856</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68731</t>
+          <t>78967</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>131799</t>
+          <t>148153</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108806</t>
+          <t>124510</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158621</t>
+          <t>174310</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>552109</t>
+          <t>598138</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>528574</t>
+          <t>574944</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>571745</t>
+          <t>617001</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>662804</t>
+          <t>663488</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>649956</t>
+          <t>648440</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>677799</t>
+          <t>676478</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1214914</t>
+          <t>1261624</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1187514</t>
+          <t>1232826</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1238979</t>
+          <t>1286002</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13902</t>
+          <t>16437</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>8960</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24600</t>
+          <t>26830</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11570</t>
+          <t>14021</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18346</t>
+          <t>21915</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>25472</t>
+          <t>30458</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15307</t>
+          <t>21864</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37390</t>
+          <t>43210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73574</t>
+          <t>82327</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38350</t>
+          <t>66052</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>103263</t>
+          <t>103577</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90080</t>
+          <t>103987</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>74941</t>
+          <t>88125</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>107251</t>
+          <t>123869</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>163654</t>
+          <t>186313</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>113263</t>
+          <t>163129</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>198113</t>
+          <t>218451</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1105388</t>
+          <t>950154</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1072599</t>
+          <t>928853</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1148332</t>
+          <t>968661</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>854917</t>
+          <t>950512</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>836692</t>
+          <t>928877</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>870884</t>
+          <t>968208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1960305</t>
+          <t>1900666</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1923304</t>
+          <t>1867543</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2023420</t>
+          <t>1925214</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>90,92%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>956567</t>
+          <t>1068520</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>956567</t>
+          <t>1068520</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>956567</t>
+          <t>1068520</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2149431</t>
+          <t>2117437</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2149431</t>
+          <t>2117437</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2149431</t>
+          <t>2117437</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>13986</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31997</t>
+          <t>27395</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12463</t>
+          <t>13899</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5416</t>
+          <t>8830</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20856</t>
+          <t>21968</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>24332</t>
+          <t>27885</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14048</t>
+          <t>18772</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38852</t>
+          <t>41930</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36270</t>
+          <t>45680</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25702</t>
+          <t>33465</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>62982</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>252520</t>
+          <t>56359</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55855</t>
+          <t>43909</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>582036</t>
+          <t>71359</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>288790</t>
+          <t>102039</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90172</t>
+          <t>84403</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>732332</t>
+          <t>124639</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>656377</t>
+          <t>742229</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>634354</t>
+          <t>722880</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>669047</t>
+          <t>757311</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>668383</t>
+          <t>742001</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>344475</t>
+          <t>725709</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>861968</t>
+          <t>756033</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1324759</t>
+          <t>1484230</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>886162</t>
+          <t>1459202</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1519288</t>
+          <t>1503573</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,15%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>19209</t>
+          <t>22386</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10890</t>
+          <t>13074</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31900</t>
+          <t>36452</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23413</t>
+          <t>23404</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14861</t>
+          <t>16210</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45341</t>
+          <t>33871</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>42621</t>
+          <t>45789</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28611</t>
+          <t>32979</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63885</t>
+          <t>60845</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>68802</t>
+          <t>79786</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52473</t>
+          <t>63539</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86253</t>
+          <t>98236</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>88836</t>
+          <t>103832</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68640</t>
+          <t>87008</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>107726</t>
+          <t>123693</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>157639</t>
+          <t>183618</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>133019</t>
+          <t>158983</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>182553</t>
+          <t>210920</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>837815</t>
+          <t>886956</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>818444</t>
+          <t>865898</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>854721</t>
+          <t>905841</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>981953</t>
+          <t>991059</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>958365</t>
+          <t>968108</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1006366</t>
+          <t>1008101</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1819769</t>
+          <t>1878015</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1789463</t>
+          <t>1848572</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1850304</t>
+          <t>1905429</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>925826</t>
+          <t>989128</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>925826</t>
+          <t>989128</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>925826</t>
+          <t>989128</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1094202</t>
+          <t>1118295</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1094202</t>
+          <t>1118295</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1094202</t>
+          <t>1118295</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2020029</t>
+          <t>2107423</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2020029</t>
+          <t>2107423</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2020029</t>
+          <t>2107423</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>52898</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>36415</t>
+          <t>45821</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>72470</t>
+          <t>79609</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>53587</t>
+          <t>58289</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39343</t>
+          <t>46237</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>74477</t>
+          <t>72479</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>106485</t>
+          <t>119243</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>83956</t>
+          <t>98452</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>132048</t>
+          <t>142678</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>254060</t>
+          <t>292218</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>196839</t>
+          <t>258210</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>290678</t>
+          <t>326608</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>487822</t>
+          <t>327905</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>286061</t>
+          <t>296155</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1100430</t>
+          <t>364719</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>741882</t>
+          <t>620124</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>533205</t>
+          <t>576867</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1399155</t>
+          <t>675168</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3151690</t>
+          <t>3177477</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3110816</t>
+          <t>3135900</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3222062</t>
+          <t>3212229</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3168056</t>
+          <t>3347059</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2564264</t>
+          <t>3309386</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3366754</t>
+          <t>3379735</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6319746</t>
+          <t>6524536</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5702669</t>
+          <t>6465687</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6531483</t>
+          <t>6576337</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3458648</t>
+          <t>3530650</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3458648</t>
+          <t>3530650</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3458648</t>
+          <t>3530650</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3709465</t>
+          <t>3733253</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3709465</t>
+          <t>3733253</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3709465</t>
+          <t>3733253</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7168113</t>
+          <t>7263903</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7168113</t>
+          <t>7263903</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7168113</t>
+          <t>7263903</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
